--- a/data/配置表/11_竞技场.xlsx
+++ b/data/配置表/11_竞技场.xlsx
@@ -1,33 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="规则表" sheetId="1" r:id="rId1"/>
-    <sheet name="层数锚点表" sheetId="2" r:id="rId2"/>
-    <sheet name="对手生成规则表" sheetId="3" r:id="rId3"/>
-    <sheet name="玩家镜像契约表" sheetId="4" r:id="rId4"/>
-    <sheet name="虚拟船长名池表" sheetId="5" r:id="rId5"/>
+    <sheet name="规则表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="层数锚点表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="对手生成规则表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="玩家镜像契约表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="虚拟船长名池表" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
+  <definedNames/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,3481 +45,3841 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="4" width="26" customWidth="1"/>
+    <col width="26" customWidth="1" min="1" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">param_key</t>
+          <t>param_key</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">value</t>
+          <t>value</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t>type</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">desc</t>
+          <t>desc</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">参数唯一key（程序按此读取）[string]</t>
+          <t>参数唯一key（程序按此读取）[string]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">参数值 [string]</t>
+          <t>参数值 [string]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">值类型 [enum] int/float/bool/string</t>
+          <t>值类型 [enum] int/float/bool/string</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">参数说明 [string]</t>
+          <t>参数说明 [string]</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">start_back_layers</t>
-        </is>
-      </c>
-      <c r="B3">
+          <t>start_back_layers</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">每次进入的起点 = max(1, 历史最高层 − 本值)。起点起的 3 层是回溯层（已通过），保底结算其奖励</t>
+          <t>每次进入的起点 = max(1, 历史最高层 − 本值)。起点起的 3 层是回溯层（已通过），保底结算其奖励</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_layer_mode</t>
+          <t>max_layer_mode</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">only_up</t>
+          <t>only_up</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">string</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">历史最高层 = 到达过的最深层（含挑战失败的那一层），只增不减；存档字段 arena_max_layer</t>
+          <t>历史最高层 = 到达过的最深层（含挑战失败的那一层），只增不减；存档字段 arena_max_layer</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">revert_reward_ratio</t>
-        </is>
-      </c>
-      <c r="B5">
+          <t>revert_reward_ratio</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>0.4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">回溯层结算比例：币与材料 ×40%；强化石与装备一律不发</t>
+          <t>回溯层结算比例：币与材料 ×40%；强化石与装备一律不发</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">revert_reward_rule</t>
+          <t>revert_reward_rule</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">no_stone_no_equip</t>
+          <t>no_stone_no_equip</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">string</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">回溯层不给强化石、不给装备；回溯层撞上 5 的倍数时装备折算普通材料 ×3，界面明写「回溯层·装备已折算」</t>
+          <t>回溯层不给强化石、不给装备；回溯层撞上 5 的倍数时装备折算普通材料 ×3，界面明写「回溯层·装备已折算」</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">food_per_member</t>
-        </is>
-      </c>
-      <c r="B7">
+          <t>food_per_member</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">每场消耗食物 = 上场人数 × 本值；无进入次数限制（频控靠起点回溯，不靠次数）</t>
+          <t>每场消耗食物 = 上场人数 × 本值；无进入次数限制（频控靠起点回溯，不靠次数）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">team_size_min</t>
-        </is>
-      </c>
-      <c r="B8">
+          <t>team_size_min</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">上场人数下限（不能全员——船还要有人开）</t>
+          <t>上场人数下限（不能全员——船还要有人开）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">team_size_max</t>
-        </is>
-      </c>
-      <c r="B9">
+          <t>team_size_max</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>3</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">上场人数上限</t>
+          <t>上场人数上限</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">lose_hp_recover</t>
-        </is>
-      </c>
-      <c r="B10">
+          <t>lose_hp_recover</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>0.3</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HP 归零判负但不死亡；本次奖励 100% 保留、历史最高层不变；回船后 HP 恢复至上限 × 本值</t>
+          <t>HP 归零判负但不死亡；本次奖励 100% 保留、历史最高层不变；回船后 HP 恢复至上限 × 本值</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">coin_base</t>
-        </is>
-      </c>
-      <c r="B11">
+          <t>coin_base</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>180</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">新层首通币 = coin_base × coin_growth^(n−1)；回溯层再 × revert_reward_ratio</t>
+          <t>新层首通币 = coin_base × coin_growth^(n−1)；回溯层再 × revert_reward_ratio</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">coin_growth</t>
-        </is>
-      </c>
-      <c r="B12">
+          <t>coin_growth</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>1.09</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">float</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">首通币逐层成长系数（竞技场币收益 &lt; 推图 210 币/分钟，定位是兑换机不是产出机）</t>
+          <t>首通币逐层成长系数（竞技场币收益 &lt; 推图 210 币/分钟，定位是兑换机不是产出机）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">stone_base</t>
-        </is>
-      </c>
-      <c r="B13">
+          <t>stone_base</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">首通强化石基础数</t>
+          <t>首通强化石基础数</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">stone_per5</t>
-        </is>
-      </c>
-      <c r="B14">
+          <t>stone_per5</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">每 5 层额外 +1 颗（第 6 层起生效）</t>
+          <t>每 5 层额外 +1 颗（第 6 层起生效）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">stone_cap</t>
-        </is>
-      </c>
-      <c r="B15">
+          <t>stone_cap</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>6</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">单层强化石封顶（26 层起固定 6 颗）</t>
+          <t>单层强化石封顶（26 层起固定 6 颗）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">equip_every5</t>
-        </is>
-      </c>
-      <c r="B16">
+          <t>equip_every5</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">n % 本值 == 0 时首通发装备 1 件；n % (本值×2) == 0 额外材料宝箱 ×1</t>
+          <t>n % 本值 == 0 时首通发装备 1 件；n % (本值×2) == 0 额外材料宝箱 ×1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">mirror_upload_top</t>
-        </is>
-      </c>
-      <c r="B17">
+          <t>mirror_upload_top</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>3</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">每名玩家上报的最强角色数；对手队伍的角色属性/外貌/名称全部来自该镜像快照</t>
+          <t>每名玩家上报的最强角色数；对手队伍的角色属性/外貌/名称全部来自该镜像快照</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">mirror_window</t>
-        </is>
-      </c>
-      <c r="B18">
+          <t>mirror_window</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">匹配窗口：只从「竞技场当前历史最高层与玩家相差 ≤ 本值」的玩家镜像里选取对手</t>
+          <t>匹配窗口：只从「竞技场当前历史最高层与玩家相差 ≤ 本值」的玩家镜像里选取对手</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">mirror_pool_size</t>
-        </is>
-      </c>
-      <c r="B19">
+          <t>mirror_pool_size</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>5</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">每次进入随机抽出的候选船长数（战前可预览职业+主属性+装备品质后挑一个打）</t>
+          <t>每次进入随机抽出的候选船长数（战前可预览职业+主属性+装备品质后挑一个打）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">mirror_fallback</t>
+          <t>mirror_fallback</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">virtual</t>
+          <t>virtual</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">string</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">窗口内真实镜像不足 mirror_pool_size 时用虚拟船长补位（属性按虚拟层的锚点公式生成，名字取名池表、外貌按 05 船员外貌表 roll）；新玩家/离线模式全部走本兜底</t>
+          <t>窗口内真实镜像不足 mirror_pool_size 时用虚拟船长补位（属性按虚拟层的锚点公式生成，名字取名池表、外貌按 05 船员外貌表 roll）；新玩家/离线模式全部走本兜底</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">virtual_layer_jitter</t>
-        </is>
-      </c>
-      <c r="B21">
+          <t>virtual_layer_jitter</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>3</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">虚拟船长的虚拟层在 [当前层 − 本值, 当前层 + 本值] 内均匀取，锚点按其虚拟层计算——保证「±3 层内」的手感不变</t>
+          <t>虚拟船长的虚拟层在 [当前层 − 本值, 当前层 + 本值] 内均匀取，锚点按其虚拟层计算——保证「±3 层内」的手感不变</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">team_size_rule</t>
+          <t>team_size_rule</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">mirror_top_n</t>
+          <t>mirror_top_n</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">string</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">对手队伍规模 = 玩家上场人数（1v1/2v2/3v3）；镜像队伍取其 chars 前 N 名（N = 玩家上场人数）</t>
+          <t>对手队伍规模 = 玩家上场人数（1v1/2v2/3v3）；镜像队伍取其 chars 前 N 名（N = 玩家上场人数）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">bias_min</t>
-        </is>
-      </c>
-      <c r="B23">
+          <t>bias_min</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
+          <t>int</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">对手四维分配至少 1 项偏科（模拟真实玩家，不是均衡木桩）；18 层起偏科数升到 2（见对手生成规则表）</t>
+          <t>对手四维分配至少 1 项偏科（模拟真实玩家，不是均衡木桩）；18 层起偏科数升到 2（见对手生成规则表）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">job_rule</t>
+          <t>job_rule</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">player_unlocked</t>
+          <t>player_unlocked</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">string</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">不生成玩家没有的职业系（避免信息不对称）</t>
+          <t>不生成玩家没有的职业系（避免信息不对称）</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">skill_rule</t>
+          <t>skill_rule</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">player_unlocked</t>
+          <t>player_unlocked</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">string</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">对手只使用玩家已解锁的技能（避免「它有你没有」的挫败）</t>
+          <t>对手只使用玩家已解锁的技能（避免「它有你没有」的挫败）</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac">
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="6" width="26" customWidth="1"/>
+    <col width="26" customWidth="1" min="1" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">layer</t>
+          <t>layer</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">base_attr</t>
+          <t>base_attr</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">opponent_attr</t>
+          <t>opponent_attr</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">pass_rate_target</t>
+          <t>pass_rate_target</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">equip_quality</t>
+          <t>equip_quality</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">desc</t>
+          <t>desc</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">层数 [int]</t>
+          <t>层数 [int]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">基准属性（单人四维合计）=100×1.11^(n−1) [int]</t>
+          <t>基准属性（单人四维合计）=100×1.11^(n−1) [int]。本表只配锚点层（1/5/10/…/50，共 11 档），段内由程序线性插值；50 层之后沿用公式外推不落表。1.11 与主线怪物成长对齐（1.75^(1/5)，决策 #32），不要改。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">对手实际属性 = base_attr×0.85 [int]</t>
+          <t>对手实际属性 = base_attr×0.85 [int]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">目标通过率（数值木桩用实际队伍实测，偏了调锚点、不调 1.11）[float]</t>
+          <t>目标通过率（数值木桩用实际队伍实测，偏了调锚点、不调 1.11）[float]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">对手装备品质档（详见对手生成规则表）[string]</t>
+          <t>对手装备品质档（详见对手生成规则表）[string]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">内容进度锚点说明 [string]</t>
+          <t>内容进度锚点说明 [string]</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>100</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>85</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>0.95</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">白/绿</t>
+          <t>白/绿</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 1 章开局（单人四维合计 100 = 标准开局船员水平）</t>
+          <t>第 1 章开局（单人四维合计 100 = 标准开局船员水平）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
+      <c r="A4" t="n">
         <v>5</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>152</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>129</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>0.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">白/绿</t>
+          <t>白/绿</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 1 章末期</t>
+          <t>第 1 章末期</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
+      <c r="A5" t="n">
         <v>10</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>256</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>218</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>0.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">蓝/紫</t>
+          <t>蓝/紫</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 2 章中期（第 8 层起对手出现紫装）</t>
+          <t>第 2 章中期（第 8 层起对手出现紫装）</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
+      <c r="A6" t="n">
         <v>15</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>431</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>366</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>0.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">蓝/紫</t>
+          <t>蓝/紫</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 2 章末期</t>
+          <t>第 2 章末期</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
+      <c r="A7" t="n">
         <v>20</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>726</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>617</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>0.55</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">全紫</t>
+          <t>全紫</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 3 章末期（第 18 层起对手全紫）</t>
+          <t>第 3 章末期（第 18 层起对手全紫）</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
+      <c r="A8" t="n">
         <v>25</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>1224</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>1040</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>0.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">全紫</t>
+          <t>全紫</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">奇迹之海第 2 层</t>
+          <t>奇迹之海第 2 层</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
+      <c r="A9" t="n">
         <v>30</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>2062</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>1753</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>0.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">全紫</t>
+          <t>全紫</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">奇迹之海第 4 层</t>
+          <t>奇迹之海第 4 层</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
+      <c r="A10" t="n">
         <v>35</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>3475</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>2954</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>0.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">全紫</t>
+          <t>全紫</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">奇迹之海第 5 层（30 层起每 5 层 ≈ 奇迹之海 1 层）</t>
+          <t>奇迹之海第 5 层（30 层起每 5 层 ≈ 奇迹之海 1 层）</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
+      <c r="A11" t="n">
         <v>40</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>5856</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>4978</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>0.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">全紫</t>
+          <t>全紫</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">奇迹之海第 6 层</t>
+          <t>奇迹之海第 6 层</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
+      <c r="A12" t="n">
         <v>45</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>9868</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>8388</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>0.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">全紫</t>
+          <t>全紫</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">奇迹之海第 7 层</t>
+          <t>奇迹之海第 7 层</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
+      <c r="A13" t="n">
         <v>50</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>16627</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>14133</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>0.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">全紫</t>
+          <t>全紫</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">奇迹之海第 8 层（50 层后沿用公式外推，不再配锚点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">说明</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">本表只配锚点层（1/5/10/…/50，共 11 档），段内由程序线性插值；50 层之后沿用公式外推不落表。1.11 与主线怪物成长对齐（1.75^(1/5)，决策 #32），不要改。</t>
-        </is>
-      </c>
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14"/>
+          <t>奇迹之海第 8 层（50 层后沿用公式外推，不再配锚点）</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="7" width="26" customWidth="1"/>
+    <col width="26" customWidth="1" min="1" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">band_id</t>
+          <t>band_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">min_layer</t>
+          <t>min_layer</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">max_layer</t>
+          <t>max_layer</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">equip_quality</t>
+          <t>equip_quality</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">equip_weights</t>
+          <t>equip_weights</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">bias_count</t>
+          <t>bias_count</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">desc</t>
+          <t>desc</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">档位唯一id [int]</t>
+          <t>档位唯一id [int]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">生效最低层（含）[int]</t>
+          <t>生效最低层（含）[int]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">生效最高层（含）；999=不设上限 [int]</t>
+          <t>生效最高层（含）；999=不设上限 [int]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">装备品质档 [string]</t>
+          <t>装备品质档 [string]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">品质权重 JSON [json]</t>
+          <t>品质权重 JSON [json]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">四维偏科项数下限 [int]</t>
+          <t>四维偏科项数下限 [int]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明 [string]</t>
+          <t>说明 [string]</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">白/绿</t>
+          <t>白/绿</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"white":70,"green":30}</t>
-        </is>
-      </c>
-      <c r="F3">
+          <t>{"white":70,"green":30}</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">开局档：第 5 层起蓝装出现率 10%（并入 green 位随机）</t>
+          <t>开局档：第 5 层起蓝装出现率 10%（并入 green 位随机）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>8</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>17</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">蓝/紫</t>
+          <t>蓝/紫</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"blue":70,"purple":30}</t>
-        </is>
-      </c>
-      <c r="F4">
+          <t>{"blue":70,"purple":30}</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 8 层起出现紫装（doc §3.4.4 口径）</t>
+          <t>第 8 层起出现紫装（doc §3.4.4 口径）</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>18</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>999</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">全紫</t>
+          <t>全紫</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"purple":100}</t>
-        </is>
-      </c>
-      <c r="F5">
+          <t>{"purple":100}</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">第 18 层起全紫，偏科更狠——高层的对手像「偏科的老玩家」，不像木桩</t>
+          <t>第 18 层起全紫，偏科更狠——高层的对手像「偏科的老玩家」，不像木桩</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="5" width="26" customWidth="1"/>
+    <col width="26" customWidth="1" min="1" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">field</t>
+          <t>field</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">type</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">required</t>
+          <t>required</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">desc</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">example</t>
+          <t>example</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">字段路径 [string]</t>
+          <t>字段路径 [string]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">类型 [string]</t>
+          <t>类型 [string]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">是否必填 [bool]</t>
+          <t>是否必填 [bool]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">说明 [string]</t>
+          <t>说明 [string]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">示例 [string]</t>
+          <t>示例 [string]</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">uid</t>
+          <t>uid</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">string</t>
-        </is>
-      </c>
-      <c r="C3">
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">玩家唯一 id（服务端生成；对手列表不展示原始 id，只展示 name）</t>
+          <t>玩家唯一 id（服务端生成；对手列表不展示原始 id，只展示 name）</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">u_88231</t>
+          <t>u_88231</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">string</t>
-        </is>
-      </c>
-      <c r="C4">
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">船长名（玩家昵称，脱敏后 ≤8 字）；虚拟船长同样从名池表取此格式</t>
+          <t>船长名（玩家昵称，脱敏后 ≤8 字）；虚拟船长同样从名池表取此格式</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">灰雾里的埃布纳</t>
+          <t>灰雾里的埃布纳</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">layer</t>
+          <t>layer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
-        </is>
-      </c>
-      <c r="C5">
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">该玩家竞技场历史最高层。匹配窗口 = 目标层 ± mirror_window(3) 层内的玩家</t>
-        </is>
-      </c>
-      <c r="E5">
+          <t>该玩家竞技场历史最高层。匹配窗口 = 目标层 ± mirror_window(3) 层内的玩家</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">chars</t>
+          <t>chars</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">json</t>
-        </is>
-      </c>
-      <c r="C6">
+          <t>json</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">最强角色数组，固定 3 名（不足 3 名不上传）；按战力降序，对手队伍按前 N 名截取（N=玩家上场人数）</t>
+          <t>最强角色数组，固定 3 名（不足 3 名不上传）；按战力降序，对手队伍按前 N 名截取（N=玩家上场人数）</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[{...},{...},{...}]</t>
+          <t>[{...},{...},{...}]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">chars[].name</t>
+          <t>chars[].name</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">string</t>
-        </is>
-      </c>
-      <c r="C7">
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">角色名（船员名，来自 05 船员名称表或玩家自定义）</t>
+          <t>角色名（船员名，来自 05 船员名称表或玩家自定义）</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">老鸦</t>
+          <t>老鸦</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">chars[].class_id</t>
+          <t>chars[].class_id</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
-        </is>
-      </c>
-      <c r="C8">
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">职业 id（引用 05 职业表）</t>
-        </is>
-      </c>
-      <c r="E8">
+          <t>职业 id（引用 05 职业表）</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>3101</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">chars[].attrs</t>
+          <t>chars[].attrs</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">json</t>
-        </is>
-      </c>
-      <c r="C9">
+          <t>json</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">四维：str=力量 / int=智力 / agi=技巧 / spr=精神</t>
+          <t>四维：str=力量 / int=智力 / agi=技巧 / spr=精神</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"str":31,"int":12,"agi":40,"spr":14}</t>
+          <t>{"str":31,"int":12,"agi":40,"spr":14}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">chars[].appearance</t>
+          <t>chars[].appearance</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">json</t>
-        </is>
-      </c>
-      <c r="C10">
+          <t>json</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">外貌，与 05 初始船员表同格式：skin 1xxx / face 2xxx / eyes 3xxx / mouth 4xxx / hair 5xxx / outfit 6xxx / accessory（0=不显示）</t>
+          <t>外貌，与 05 初始船员表同格式：skin 1xxx / face 2xxx / eyes 3xxx / mouth 4xxx / hair 5xxx / outfit 6xxx / accessory（0=不显示）</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"skin":1002,"face":2005,"eyes":3003,"mouth":4001,"hair":5007,"outfit":6004,"accessory":0}</t>
+          <t>{"skin":1002,"face":2005,"eyes":3003,"mouth":4001,"hair":5007,"outfit":6004,"accessory":0}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">chars[].equip</t>
+          <t>chars[].equip</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">json</t>
-        </is>
-      </c>
-      <c r="C11">
+          <t>json</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">装备位摘要（06 装备：id / 品质 / 词缀），只够战力预估与品质展示，不还原完整装备树</t>
+          <t>装备位摘要（06 装备：id / 品质 / 词缀），只够战力预估与品质展示，不还原完整装备树</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[{"id":2001,"quality":"blue"}]</t>
+          <t>[{"id":2001,"quality":"blue"}]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">chars[].skills</t>
+          <t>chars[].skills</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">json</t>
-        </is>
-      </c>
-      <c r="C12">
+          <t>json</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">技能 id 列表（≤4，只含玩家已解锁技能，与 skill_rule 一致）</t>
+          <t>技能 id 列表（≤4，只含玩家已解锁技能，与 skill_rule 一致）</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[5101,5102]</t>
+          <t>[5101,5102]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ts</t>
+          <t>ts</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
-        </is>
-      </c>
-      <c r="C13">
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">快照时间戳；每次历史最高层变化 / 上阵阵容变化 / 装备变化时全量重传</t>
-        </is>
-      </c>
-      <c r="E13">
+          <t>快照时间戳；每次历史最高层变化 / 上阵阵容变化 / 装备变化时全量重传</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
         <v>1790000000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ver</t>
+          <t>ver</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">int</t>
-        </is>
-      </c>
-      <c r="C14">
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">契约版本号，当前 1；服务端按版本兼容旧快照</t>
-        </is>
-      </c>
-      <c r="E14">
+          <t>契约版本号，当前 1；服务端按版本兼容旧快照</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D102"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="4" width="26" customWidth="1"/>
+    <col width="26" customWidth="1" min="1" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t xml:space="preserve">npc_id</t>
+          <t>npc_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">name</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">gender</t>
+          <t>gender</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">quip</t>
+          <t>quip</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">虚拟船长唯一id [int]</t>
+          <t>虚拟船长唯一id [int]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">船长假名（称号 + 名，营造「和其他船长打」的感觉；匹配时随机去重抽取）[string]</t>
+          <t>船长假名（称号 + 名，营造「和其他船长打」的感觉；匹配时随机去重抽取）[string]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">性别（决定外貌 roll 的部位池，引用 05 船员外貌表 gender 列）[enum] male/female</t>
+          <t>性别（决定外貌 roll 的部位池，引用 05 船员外貌表 gender 列）[enum] male/female</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">名池备注/口癖，战前预览页可展示 [string]</t>
+          <t>名池备注/口癖，战前预览页可展示 [string]</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">独眼的老巴罗</t>
+          <t>独眼的老巴罗</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">总是先看天气，再看人。</t>
+          <t>总是先看天气，再看人。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">独眼的埃布纳</t>
+          <t>独眼的埃布纳</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">总是先看天气，再看人。</t>
+          <t>总是先看天气，再看人。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">独眼的霍尔格</t>
+          <t>独眼的霍尔格</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">总是先看天气，再看人。</t>
+          <t>总是先看天气，再看人。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">独眼的铁手皮特</t>
+          <t>独眼的铁手皮特</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">总是先看天气，再看人。</t>
+          <t>总是先看天气，再看人。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">独眼的哑巴扬</t>
+          <t>独眼的哑巴扬</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">总是先看天气，再看人。</t>
+          <t>总是先看天气，再看人。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">独眼的玛尔戈</t>
+          <t>独眼的玛尔戈</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">总是先看天气，再看人。</t>
+          <t>总是先看天气，再看人。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">独眼的寡妇妮丝</t>
+          <t>独眼的寡妇妮丝</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">总是先看天气，再看人。</t>
+          <t>总是先看天气，再看人。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
+      <c r="A10" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">独眼的烧不坏的薇拉</t>
+          <t>独眼的烧不坏的薇拉</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">总是先看天气，再看人。</t>
+          <t>总是先看天气，再看人。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
+      <c r="A11" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">独眼的数钱的萝丝</t>
+          <t>独眼的数钱的萝丝</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">总是先看天气，再看人。</t>
+          <t>总是先看天气，再看人。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">独眼的雾里的小满</t>
+          <t>独眼的雾里的小满</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">总是先看天气，再看人。</t>
+          <t>总是先看天气，再看人。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">灰雾里的老巴罗</t>
+          <t>灰雾里的老巴罗</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">船是捡的，名字是自己起的。</t>
+          <t>船是捡的，名字是自己起的。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
+      <c r="A14" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">灰雾里的埃布纳</t>
+          <t>灰雾里的埃布纳</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">船是捡的，名字是自己起的。</t>
+          <t>船是捡的，名字是自己起的。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
+      <c r="A15" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">灰雾里的霍尔格</t>
+          <t>灰雾里的霍尔格</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">船是捡的，名字是自己起的。</t>
+          <t>船是捡的，名字是自己起的。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
+      <c r="A16" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">灰雾里的铁手皮特</t>
+          <t>灰雾里的铁手皮特</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">船是捡的，名字是自己起的。</t>
+          <t>船是捡的，名字是自己起的。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
+      <c r="A17" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">灰雾里的哑巴扬</t>
+          <t>灰雾里的哑巴扬</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">船是捡的，名字是自己起的。</t>
+          <t>船是捡的，名字是自己起的。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
+      <c r="A18" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">灰雾里的玛尔戈</t>
+          <t>灰雾里的玛尔戈</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">船是捡的，名字是自己起的。</t>
+          <t>船是捡的，名字是自己起的。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
+      <c r="A19" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">灰雾里的寡妇妮丝</t>
+          <t>灰雾里的寡妇妮丝</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">船是捡的，名字是自己起的。</t>
+          <t>船是捡的，名字是自己起的。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
+      <c r="A20" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">灰雾里的烧不坏的薇拉</t>
+          <t>灰雾里的烧不坏的薇拉</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">船是捡的，名字是自己起的。</t>
+          <t>船是捡的，名字是自己起的。</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
+      <c r="A21" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">灰雾里的数钱的萝丝</t>
+          <t>灰雾里的数钱的萝丝</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">船是捡的，名字是自己起的。</t>
+          <t>船是捡的，名字是自己起的。</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
+      <c r="A22" t="n">
         <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">灰雾里的雾里的小满</t>
+          <t>灰雾里的雾里的小满</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">船是捡的，名字是自己起的。</t>
+          <t>船是捡的，名字是自己起的。</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
+      <c r="A23" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">不睡觉的老巴罗</t>
+          <t>不睡觉的老巴罗</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">据说把当年的船员都忘了。</t>
+          <t>据说把当年的船员都忘了。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
+      <c r="A24" t="n">
         <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">不睡觉的埃布纳</t>
+          <t>不睡觉的埃布纳</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">据说把当年的船员都忘了。</t>
+          <t>据说把当年的船员都忘了。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
+      <c r="A25" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">不睡觉的霍尔格</t>
+          <t>不睡觉的霍尔格</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">据说把当年的船员都忘了。</t>
+          <t>据说把当年的船员都忘了。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
+      <c r="A26" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">不睡觉的铁手皮特</t>
+          <t>不睡觉的铁手皮特</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">据说把当年的船员都忘了。</t>
+          <t>据说把当年的船员都忘了。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
+      <c r="A27" t="n">
         <v>25</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">不睡觉的哑巴扬</t>
+          <t>不睡觉的哑巴扬</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">据说把当年的船员都忘了。</t>
+          <t>据说把当年的船员都忘了。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
+      <c r="A28" t="n">
         <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">不睡觉的玛尔戈</t>
+          <t>不睡觉的玛尔戈</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">据说把当年的船员都忘了。</t>
+          <t>据说把当年的船员都忘了。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
+      <c r="A29" t="n">
         <v>27</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">不睡觉的寡妇妮丝</t>
+          <t>不睡觉的寡妇妮丝</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">据说把当年的船员都忘了。</t>
+          <t>据说把当年的船员都忘了。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
+      <c r="A30" t="n">
         <v>28</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">不睡觉的烧不坏的薇拉</t>
+          <t>不睡觉的烧不坏的薇拉</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">据说把当年的船员都忘了。</t>
+          <t>据说把当年的船员都忘了。</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
+      <c r="A31" t="n">
         <v>29</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">不睡觉的数钱的萝丝</t>
+          <t>不睡觉的数钱的萝丝</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">据说把当年的船员都忘了。</t>
+          <t>据说把当年的船员都忘了。</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
+      <c r="A32" t="n">
         <v>30</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">不睡觉的雾里的小满</t>
+          <t>不睡觉的雾里的小满</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">据说把当年的船员都忘了。</t>
+          <t>据说把当年的船员都忘了。</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
+      <c r="A33" t="n">
         <v>31</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">欠着债的老巴罗</t>
+          <t>欠着债的老巴罗</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">欠遍了半个海域的债。</t>
+          <t>欠遍了半个海域的债。</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
+      <c r="A34" t="n">
         <v>32</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">欠着债的埃布纳</t>
+          <t>欠着债的埃布纳</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">欠遍了半个海域的债。</t>
+          <t>欠遍了半个海域的债。</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
+      <c r="A35" t="n">
         <v>33</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">欠着债的霍尔格</t>
+          <t>欠着债的霍尔格</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">欠遍了半个海域的债。</t>
+          <t>欠遍了半个海域的债。</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
+      <c r="A36" t="n">
         <v>34</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">欠着债的铁手皮特</t>
+          <t>欠着债的铁手皮特</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">欠遍了半个海域的债。</t>
+          <t>欠遍了半个海域的债。</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
+      <c r="A37" t="n">
         <v>35</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">欠着债的哑巴扬</t>
+          <t>欠着债的哑巴扬</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">欠遍了半个海域的债。</t>
+          <t>欠遍了半个海域的债。</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
+      <c r="A38" t="n">
         <v>36</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">欠着债的玛尔戈</t>
+          <t>欠着债的玛尔戈</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">欠遍了半个海域的债。</t>
+          <t>欠遍了半个海域的债。</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
+      <c r="A39" t="n">
         <v>37</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">欠着债的寡妇妮丝</t>
+          <t>欠着债的寡妇妮丝</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">欠遍了半个海域的债。</t>
+          <t>欠遍了半个海域的债。</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
+      <c r="A40" t="n">
         <v>38</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">欠着债的烧不坏的薇拉</t>
+          <t>欠着债的烧不坏的薇拉</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">欠遍了半个海域的债。</t>
+          <t>欠遍了半个海域的债。</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
+      <c r="A41" t="n">
         <v>39</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">欠着债的数钱的萝丝</t>
+          <t>欠着债的数钱的萝丝</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">欠遍了半个海域的债。</t>
+          <t>欠遍了半个海域的债。</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
+      <c r="A42" t="n">
         <v>40</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">欠着债的雾里的小满</t>
+          <t>欠着债的雾里的小满</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">欠遍了半个海域的债。</t>
+          <t>欠遍了半个海域的债。</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
+      <c r="A43" t="n">
         <v>41</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">镀过金的老巴罗</t>
+          <t>镀过金的老巴罗</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">金牙是唯一没泡过海水的东西。</t>
+          <t>金牙是唯一没泡过海水的东西。</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
+      <c r="A44" t="n">
         <v>42</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">镀过金的埃布纳</t>
+          <t>镀过金的埃布纳</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">金牙是唯一没泡过海水的东西。</t>
+          <t>金牙是唯一没泡过海水的东西。</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
+      <c r="A45" t="n">
         <v>43</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">镀过金的霍尔格</t>
+          <t>镀过金的霍尔格</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">金牙是唯一没泡过海水的东西。</t>
+          <t>金牙是唯一没泡过海水的东西。</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
+      <c r="A46" t="n">
         <v>44</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">镀过金的铁手皮特</t>
+          <t>镀过金的铁手皮特</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">金牙是唯一没泡过海水的东西。</t>
+          <t>金牙是唯一没泡过海水的东西。</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
+      <c r="A47" t="n">
         <v>45</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">镀过金的哑巴扬</t>
+          <t>镀过金的哑巴扬</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">金牙是唯一没泡过海水的东西。</t>
+          <t>金牙是唯一没泡过海水的东西。</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
+      <c r="A48" t="n">
         <v>46</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">镀过金的玛尔戈</t>
+          <t>镀过金的玛尔戈</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">金牙是唯一没泡过海水的东西。</t>
+          <t>金牙是唯一没泡过海水的东西。</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
+      <c r="A49" t="n">
         <v>47</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">镀过金的寡妇妮丝</t>
+          <t>镀过金的寡妇妮丝</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">金牙是唯一没泡过海水的东西。</t>
+          <t>金牙是唯一没泡过海水的东西。</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
+      <c r="A50" t="n">
         <v>48</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">镀过金的烧不坏的薇拉</t>
+          <t>镀过金的烧不坏的薇拉</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">金牙是唯一没泡过海水的东西。</t>
+          <t>金牙是唯一没泡过海水的东西。</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
+      <c r="A51" t="n">
         <v>49</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">镀过金的数钱的萝丝</t>
+          <t>镀过金的数钱的萝丝</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">金牙是唯一没泡过海水的东西。</t>
+          <t>金牙是唯一没泡过海水的东西。</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
+      <c r="A52" t="n">
         <v>50</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">镀过金的雾里的小满</t>
+          <t>镀过金的雾里的小满</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">金牙是唯一没泡过海水的东西。</t>
+          <t>金牙是唯一没泡过海水的东西。</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53">
+      <c r="A53" t="n">
         <v>51</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">失眠的老巴罗</t>
+          <t>失眠的老巴罗</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">三年没在陆地上睡过觉。</t>
+          <t>三年没在陆地上睡过觉。</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54">
+      <c r="A54" t="n">
         <v>52</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">失眠的埃布纳</t>
+          <t>失眠的埃布纳</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">三年没在陆地上睡过觉。</t>
+          <t>三年没在陆地上睡过觉。</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55">
+      <c r="A55" t="n">
         <v>53</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">失眠的霍尔格</t>
+          <t>失眠的霍尔格</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">三年没在陆地上睡过觉。</t>
+          <t>三年没在陆地上睡过觉。</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56">
+      <c r="A56" t="n">
         <v>54</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">失眠的铁手皮特</t>
+          <t>失眠的铁手皮特</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">三年没在陆地上睡过觉。</t>
+          <t>三年没在陆地上睡过觉。</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57">
+      <c r="A57" t="n">
         <v>55</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">失眠的哑巴扬</t>
+          <t>失眠的哑巴扬</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">三年没在陆地上睡过觉。</t>
+          <t>三年没在陆地上睡过觉。</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58">
+      <c r="A58" t="n">
         <v>56</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">失眠的玛尔戈</t>
+          <t>失眠的玛尔戈</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">三年没在陆地上睡过觉。</t>
+          <t>三年没在陆地上睡过觉。</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59">
+      <c r="A59" t="n">
         <v>57</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">失眠的寡妇妮丝</t>
+          <t>失眠的寡妇妮丝</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">三年没在陆地上睡过觉。</t>
+          <t>三年没在陆地上睡过觉。</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60">
+      <c r="A60" t="n">
         <v>58</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">失眠的烧不坏的薇拉</t>
+          <t>失眠的烧不坏的薇拉</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">三年没在陆地上睡过觉。</t>
+          <t>三年没在陆地上睡过觉。</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61">
+      <c r="A61" t="n">
         <v>59</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">失眠的数钱的萝丝</t>
+          <t>失眠的数钱的萝丝</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">三年没在陆地上睡过觉。</t>
+          <t>三年没在陆地上睡过觉。</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62">
+      <c r="A62" t="n">
         <v>60</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">失眠的雾里的小满</t>
+          <t>失眠的雾里的小满</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">三年没在陆地上睡过觉。</t>
+          <t>三年没在陆地上睡过觉。</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63">
+      <c r="A63" t="n">
         <v>61</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">活下来的老巴罗</t>
+          <t>活下来的老巴罗</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">沉过四次船，每次都说是最后一次。</t>
+          <t>沉过四次船，每次都说是最后一次。</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64">
+      <c r="A64" t="n">
         <v>62</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">活下来的埃布纳</t>
+          <t>活下来的埃布纳</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">沉过四次船，每次都说是最后一次。</t>
+          <t>沉过四次船，每次都说是最后一次。</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65">
+      <c r="A65" t="n">
         <v>63</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">活下来的霍尔格</t>
+          <t>活下来的霍尔格</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">沉过四次船，每次都说是最后一次。</t>
+          <t>沉过四次船，每次都说是最后一次。</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66">
+      <c r="A66" t="n">
         <v>64</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">活下来的铁手皮特</t>
+          <t>活下来的铁手皮特</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">沉过四次船，每次都说是最后一次。</t>
+          <t>沉过四次船，每次都说是最后一次。</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67">
+      <c r="A67" t="n">
         <v>65</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">活下来的哑巴扬</t>
+          <t>活下来的哑巴扬</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">沉过四次船，每次都说是最后一次。</t>
+          <t>沉过四次船，每次都说是最后一次。</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68">
+      <c r="A68" t="n">
         <v>66</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">活下来的玛尔戈</t>
+          <t>活下来的玛尔戈</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">沉过四次船，每次都说是最后一次。</t>
+          <t>沉过四次船，每次都说是最后一次。</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69">
+      <c r="A69" t="n">
         <v>67</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">活下来的寡妇妮丝</t>
+          <t>活下来的寡妇妮丝</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">沉过四次船，每次都说是最后一次。</t>
+          <t>沉过四次船，每次都说是最后一次。</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70">
+      <c r="A70" t="n">
         <v>68</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">活下来的烧不坏的薇拉</t>
+          <t>活下来的烧不坏的薇拉</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">沉过四次船，每次都说是最后一次。</t>
+          <t>沉过四次船，每次都说是最后一次。</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71">
+      <c r="A71" t="n">
         <v>69</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">活下来的数钱的萝丝</t>
+          <t>活下来的数钱的萝丝</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">沉过四次船，每次都说是最后一次。</t>
+          <t>沉过四次船，每次都说是最后一次。</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72">
+      <c r="A72" t="n">
         <v>70</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">活下来的雾里的小满</t>
+          <t>活下来的雾里的小满</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">沉过四次船，每次都说是最后一次。</t>
+          <t>沉过四次船，每次都说是最后一次。</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73">
+      <c r="A73" t="n">
         <v>71</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">说谎的老巴罗</t>
+          <t>说谎的老巴罗</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">说过的话一半是编的。</t>
+          <t>说过的话一半是编的。</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74">
+      <c r="A74" t="n">
         <v>72</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">说谎的埃布纳</t>
+          <t>说谎的埃布纳</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">说过的话一半是编的。</t>
+          <t>说过的话一半是编的。</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75">
+      <c r="A75" t="n">
         <v>73</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">说谎的霍尔格</t>
+          <t>说谎的霍尔格</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">说过的话一半是编的。</t>
+          <t>说过的话一半是编的。</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76">
+      <c r="A76" t="n">
         <v>74</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">说谎的铁手皮特</t>
+          <t>说谎的铁手皮特</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">说过的话一半是编的。</t>
+          <t>说过的话一半是编的。</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77">
+      <c r="A77" t="n">
         <v>75</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">说谎的哑巴扬</t>
+          <t>说谎的哑巴扬</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">说过的话一半是编的。</t>
+          <t>说过的话一半是编的。</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78">
+      <c r="A78" t="n">
         <v>76</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">说谎的玛尔戈</t>
+          <t>说谎的玛尔戈</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">说过的话一半是编的。</t>
+          <t>说过的话一半是编的。</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79">
+      <c r="A79" t="n">
         <v>77</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">说谎的寡妇妮丝</t>
+          <t>说谎的寡妇妮丝</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">说过的话一半是编的。</t>
+          <t>说过的话一半是编的。</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80">
+      <c r="A80" t="n">
         <v>78</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">说谎的烧不坏的薇拉</t>
+          <t>说谎的烧不坏的薇拉</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">说过的话一半是编的。</t>
+          <t>说过的话一半是编的。</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81">
+      <c r="A81" t="n">
         <v>79</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">说谎的数钱的萝丝</t>
+          <t>说谎的数钱的萝丝</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">说过的话一半是编的。</t>
+          <t>说过的话一半是编的。</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82">
+      <c r="A82" t="n">
         <v>80</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">说谎的雾里的小满</t>
+          <t>说谎的雾里的小满</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">说过的话一半是编的。</t>
+          <t>说过的话一半是编的。</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83">
+      <c r="A83" t="n">
         <v>81</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">数星星的老巴罗</t>
+          <t>数星星的老巴罗</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">会在甲板上给星星记账。</t>
+          <t>会在甲板上给星星记账。</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84">
+      <c r="A84" t="n">
         <v>82</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">数星星的埃布纳</t>
+          <t>数星星的埃布纳</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">会在甲板上给星星记账。</t>
+          <t>会在甲板上给星星记账。</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85">
+      <c r="A85" t="n">
         <v>83</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">数星星的霍尔格</t>
+          <t>数星星的霍尔格</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">会在甲板上给星星记账。</t>
+          <t>会在甲板上给星星记账。</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86">
+      <c r="A86" t="n">
         <v>84</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t xml:space="preserve">数星星的铁手皮特</t>
+          <t>数星星的铁手皮特</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">会在甲板上给星星记账。</t>
+          <t>会在甲板上给星星记账。</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87">
+      <c r="A87" t="n">
         <v>85</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t xml:space="preserve">数星星的哑巴扬</t>
+          <t>数星星的哑巴扬</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">会在甲板上给星星记账。</t>
+          <t>会在甲板上给星星记账。</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88">
+      <c r="A88" t="n">
         <v>86</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t xml:space="preserve">数星星的玛尔戈</t>
+          <t>数星星的玛尔戈</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">会在甲板上给星星记账。</t>
+          <t>会在甲板上给星星记账。</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89">
+      <c r="A89" t="n">
         <v>87</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">数星星的寡妇妮丝</t>
+          <t>数星星的寡妇妮丝</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">会在甲板上给星星记账。</t>
+          <t>会在甲板上给星星记账。</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90">
+      <c r="A90" t="n">
         <v>88</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">数星星的烧不坏的薇拉</t>
+          <t>数星星的烧不坏的薇拉</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">会在甲板上给星星记账。</t>
+          <t>会在甲板上给星星记账。</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91">
+      <c r="A91" t="n">
         <v>89</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">数星星的数钱的萝丝</t>
+          <t>数星星的数钱的萝丝</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">会在甲板上给星星记账。</t>
+          <t>会在甲板上给星星记账。</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92">
+      <c r="A92" t="n">
         <v>90</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">数星星的雾里的小满</t>
+          <t>数星星的雾里的小满</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">会在甲板上给星星记账。</t>
+          <t>会在甲板上给星星记账。</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93">
+      <c r="A93" t="n">
         <v>91</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">改了名的老巴罗</t>
+          <t>改了名的老巴罗</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">上个月还叫别的名字。</t>
+          <t>上个月还叫别的名字。</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94">
+      <c r="A94" t="n">
         <v>92</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t xml:space="preserve">改了名的埃布纳</t>
+          <t>改了名的埃布纳</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">上个月还叫别的名字。</t>
+          <t>上个月还叫别的名字。</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95">
+      <c r="A95" t="n">
         <v>93</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t xml:space="preserve">改了名的霍尔格</t>
+          <t>改了名的霍尔格</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">上个月还叫别的名字。</t>
+          <t>上个月还叫别的名字。</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96">
+      <c r="A96" t="n">
         <v>94</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">改了名的铁手皮特</t>
+          <t>改了名的铁手皮特</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">上个月还叫别的名字。</t>
+          <t>上个月还叫别的名字。</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97">
+      <c r="A97" t="n">
         <v>95</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">改了名的哑巴扬</t>
+          <t>改了名的哑巴扬</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">male</t>
+          <t>male</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">上个月还叫别的名字。</t>
+          <t>上个月还叫别的名字。</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98">
+      <c r="A98" t="n">
         <v>96</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">改了名的玛尔戈</t>
+          <t>改了名的玛尔戈</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">上个月还叫别的名字。</t>
+          <t>上个月还叫别的名字。</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99">
+      <c r="A99" t="n">
         <v>97</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">改了名的寡妇妮丝</t>
+          <t>改了名的寡妇妮丝</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">上个月还叫别的名字。</t>
+          <t>上个月还叫别的名字。</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100">
+      <c r="A100" t="n">
         <v>98</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">改了名的烧不坏的薇拉</t>
+          <t>改了名的烧不坏的薇拉</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">上个月还叫别的名字。</t>
+          <t>上个月还叫别的名字。</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101">
+      <c r="A101" t="n">
         <v>99</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">改了名的数钱的萝丝</t>
+          <t>改了名的数钱的萝丝</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">上个月还叫别的名字。</t>
+          <t>上个月还叫别的名字。</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102">
+      <c r="A102" t="n">
         <v>100</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">改了名的雾里的小满</t>
+          <t>改了名的雾里的小满</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">female</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">上个月还叫别的名字。</t>
+          <t>上个月还叫别的名字。</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>